--- a/experiments/results/cabp/cplex-cp-cabp.xlsx
+++ b/experiments/results/cabp/cplex-cp-cabp.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x0.75" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1.25" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1.5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="cabp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cabp_x0.5_has_hole" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cabp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cabp_x0.75_has_hole" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="cabp_x1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="cabp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="cabp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,66 +419,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -540,17 +535,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -602,17 +600,20 @@
           <t>16</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -664,17 +665,20 @@
           <t>18</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -726,17 +730,20 @@
           <t>24</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>12.6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -788,17 +795,20 @@
           <t>24</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>23</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -850,17 +860,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.13</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -912,17 +925,20 @@
           <t>25</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -974,17 +990,20 @@
           <t>24</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>21.8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>30.34</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1036,17 +1055,20 @@
           <t>40</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>39</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>15.5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1098,17 +1120,20 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="n">
+        <v>49</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>208.3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1156,17 +1181,20 @@
           <t>56</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>7.88</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1218,17 +1246,20 @@
           <t>56</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>15.8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1280,17 +1311,20 @@
           <t>194</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="n">
+        <v>193</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>218.2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1338,17 +1372,20 @@
           <t>194</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="n">
+        <v>193</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>218.9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1396,17 +1433,20 @@
           <t>208</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="n">
+        <v>207</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>93.7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>27.95</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1458,17 +1498,20 @@
           <t>219</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="n">
+        <v>218</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>160.8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>1800.06</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1516,17 +1559,20 @@
           <t>246</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>245</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>60.4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1578,17 +1624,20 @@
           <t>248</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>247</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>205.5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1636,17 +1685,20 @@
           <t>268</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="n">
+        <v>267</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>170.7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1694,17 +1746,20 @@
           <t>284</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="n">
+        <v>283</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>236.5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>1800.06</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1752,17 +1807,20 @@
           <t>328</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="n">
+        <v>327</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>132.1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>42.28</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1814,17 +1872,20 @@
           <t>337</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>336</v>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>217.6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1872,17 +1933,20 @@
           <t>342</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>341</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>233.0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1930,17 +1994,20 @@
           <t>300</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>299</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>309.1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1953,66 +2020,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2041,40 +2113,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2103,40 +2178,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10.6</t>
-        </is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2165,40 +2243,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>17</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2227,40 +2308,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>13.2</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>23</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2289,40 +2373,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>23</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2351,40 +2438,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2413,40 +2503,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>11.9</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2475,40 +2568,43 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>53.4</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>254.77</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>47.72</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2537,40 +2633,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>39</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2599,40 +2698,47 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>167.5</t>
-        </is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>47</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2657,40 +2763,47 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>149.5</t>
-        </is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>55</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2715,40 +2828,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>55</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2777,40 +2893,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>254.4</t>
-        </is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>191</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>195.6</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2835,40 +2954,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>254.0</t>
-        </is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>191</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>195.5</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2893,40 +3015,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>117.2</t>
-        </is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>207</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>84.06</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2955,40 +3080,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>186.8</t>
-        </is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>213</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>150.1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3013,40 +3141,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>246</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>245</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3075,40 +3206,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>230.3</t>
-        </is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>247</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.07</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3133,40 +3267,47 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>130</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>273</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>259</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>196.8</t>
-        </is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>258</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3191,40 +3332,47 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>57</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>282.8</t>
-        </is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>224</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>126.2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>53.84</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3249,40 +3397,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>328</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>206.0</t>
-        </is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>327</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>172.30</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>50.25</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3311,40 +3462,47 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>329</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>242.5</t>
-        </is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>328</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1800.11</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3369,40 +3527,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>58</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>157</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>392.9</t>
-        </is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>341</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.10</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>196.5</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3427,40 +3588,43 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>147</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>366.7</t>
-        </is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>299</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.08</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>245.6</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.11</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3473,66 +3637,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3561,40 +3730,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3623,40 +3795,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>23</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3685,40 +3860,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3747,40 +3925,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>35</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3809,40 +3990,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>35</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3871,40 +4055,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>34</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3933,40 +4120,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>39</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -3995,40 +4185,43 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>274.6</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>39</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1566.61</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>254.77</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4057,40 +4250,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>59</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>6.97</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4119,44 +4315,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4181,44 +4376,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>83</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28.40</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4243,40 +4437,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>83</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4305,40 +4502,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>237.5</t>
-        </is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>312</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>254.4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4363,40 +4563,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>237.7</t>
-        </is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>312</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.03</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>254.0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4421,40 +4624,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>312</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>102.6</t>
-        </is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>311</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>96.72</t>
+          <t>117.2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>84.06</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4483,40 +4689,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>212.9</t>
-        </is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>328</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>186.8</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.03</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4541,40 +4750,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>369</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>368</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4603,40 +4815,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>238.7</t>
-        </is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>375</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.05</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>230.3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.03</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4661,44 +4876,45 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>194</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>387</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>196.8</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4723,44 +4939,43 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>203.0</t>
-        </is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>423</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>406.61</t>
+          <t>282.8</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4785,40 +5000,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>496</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>492</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>119.7</t>
-        </is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>491</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>122.68</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>172.30</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -4847,44 +5065,45 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>493</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>242.5</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.11</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4909,40 +5128,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>274.8</t>
-        </is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>509</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>392.9</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.10</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4967,40 +5189,43 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>315.4</t>
-        </is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>456</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>366.7</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.08</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5013,66 +5238,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -5101,40 +5331,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5163,40 +5396,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>19.3</t>
-        </is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>23</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31.31</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5225,40 +5461,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5287,40 +5526,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>35</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5349,40 +5591,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>35</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5411,40 +5656,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>34</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5473,40 +5721,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>39</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5535,40 +5786,47 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>301.2</t>
-        </is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>39</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>524.49</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5593,40 +5851,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>59</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5655,40 +5916,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>71</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5717,40 +5981,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>81</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>12.49</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5779,40 +6046,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>83</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -5841,40 +6111,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>264.6</t>
-        </is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>287</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>210.4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.08</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5899,40 +6172,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>264.5</t>
-        </is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>287</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.07</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5957,40 +6233,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>312</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>103.6</t>
-        </is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>311</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>87.84</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>77.84</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6019,40 +6298,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>66</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>222.6</t>
-        </is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>324</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>175.7</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.07</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6077,40 +6359,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>369</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>368</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6139,40 +6424,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>377</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>262.1</t>
-        </is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>367</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>201.3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6197,40 +6485,43 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>194</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>387</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>386</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6259,40 +6550,43 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>337</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>254.2</t>
-        </is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>336</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>879.45</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>173.13</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6321,40 +6615,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>124</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>496</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>492</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>167.4</t>
-        </is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>491</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>306.77</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>123.91</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6383,40 +6680,43 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>493</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>492</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6445,40 +6745,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>852</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>295.3</t>
-        </is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>509</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>229.0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6503,40 +6806,43 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>347.5</t>
-        </is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>449</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>281.2</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.08</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6549,66 +6855,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -6637,40 +6948,43 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6699,40 +7013,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>31</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>57.65</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>11.75</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6761,40 +7078,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>38</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6823,40 +7143,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>16.3</t>
-        </is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>47</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14.50</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6885,40 +7208,43 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>47</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -6947,40 +7273,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>49</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7009,40 +7338,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>54</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7071,40 +7403,47 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>292.7</t>
-        </is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>274.6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1566.61</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7129,40 +7468,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>83</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7191,40 +7533,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>95</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7253,40 +7598,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>110</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>70.16</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>28.40</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7315,40 +7663,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>115</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7377,40 +7728,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>287.2</t>
-        </is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>395</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>237.5</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7435,40 +7789,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>287.1</t>
-        </is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>395</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1800.01</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>237.7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.03</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7493,40 +7850,43 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>420</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>125.4</t>
-        </is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>419</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>207.43</t>
+          <t>102.6</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>96.72</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7555,40 +7915,43 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>445</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>258.2</t>
-        </is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>433</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>212.9</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7613,40 +7976,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>165</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>494</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>492</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>46.3</t>
-        </is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>491</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7675,40 +8041,43 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>277.3</t>
-        </is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>495</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1800.04</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>238.7</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.05</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7733,40 +8102,43 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>258</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>546</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>517</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>516</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7795,40 +8167,43 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>114</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>453</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>281.1</t>
-        </is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>452</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>998.50</t>
+          <t>203.0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>406.61</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7857,40 +8232,43 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>166</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>662</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>660</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>988</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>196.0</t>
-        </is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>659</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>439.38</t>
+          <t>119.7</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>122.68</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7919,40 +8297,43 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>328</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>329</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>675</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>657</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>656</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -7981,40 +8362,43 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>685</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>329.5</t>
-        </is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>683</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>274.8</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8039,6 +8423,3232 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>605</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>315.4</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Time limit (s)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Best bound</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Best objective</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Time consumed (s)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>28</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>39</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>31.31</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>47</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>59</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5.55</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>59</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>59</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>64</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>63</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>301.2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>103</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>119</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>136</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>45.47</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>143</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>17.1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>491</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>264.6</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>491</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>264.5</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.07</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>523</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>103.6</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>87.84</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>460</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>222.6</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>614</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>615</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>262.1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>644</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>564</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>254.2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>879.45</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>823</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>167.4</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>306.77</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>820</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>851</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>295.3</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>755</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>347.5</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Time limit (s)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Best bound</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Best objective</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Time consumed (s)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>36</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>47</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>57.65</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>56</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>71</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>16.3</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>14.50</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>71</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>74</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>79</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>79</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>292.7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>123</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>143</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>165</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>70.16</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>171</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>587</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>287.2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>587</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>287.1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>627</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>125.4</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>207.43</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>649</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>258.2</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>737</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>743</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>277.3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.04</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>774</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>676</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>281.1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>998.50</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>987</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>196.0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>439.38</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>984</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1025</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>329.5</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
@@ -8062,17 +11672,20 @@
           <t>906</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>905</v>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>365.2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/experiments/results/cabp/cplex-cp-cabp.xlsx
+++ b/experiments/results/cabp/cplex-cp-cabp.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cabp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cabp_x0.5_has_hole" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cabp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cabp_x0.75_has_hole" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cabp_x1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="cabp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cabp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x0.5_no_hole" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x0.75_no_hole" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,67 +435,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -540,12 +552,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -610,7 +622,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -670,12 +682,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -735,12 +747,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -800,7 +812,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -865,12 +877,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -930,12 +942,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -995,12 +1007,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1060,12 +1072,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1117,23 +1129,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>208.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1186,12 +1202,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1251,12 +1267,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1308,15 +1324,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>192</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>218.2</t>
+          <t>195.6</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1369,20 +1385,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>192</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>218.9</t>
+          <t>195.5</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1438,12 +1454,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1490,25 +1506,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>160.8</t>
+          <t>150.1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1564,12 +1580,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1629,12 +1645,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.07</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -1682,23 +1698,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>170.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1738,28 +1758,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>225</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>236.5</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>53.84</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1812,12 +1836,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>132.1</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>50.25</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1869,23 +1893,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>217.6</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1925,7 +1953,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>157</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1938,12 +1966,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>233.0</t>
+          <t>196.5</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -1986,7 +2014,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1999,12 +2027,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>309.1</t>
+          <t>245.6</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1800.00</t>
+          <t>1800.11</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2024,67 +2052,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2141,12 +2169,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -2211,7 +2239,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -2271,12 +2299,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2336,12 +2364,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2401,7 +2429,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2466,12 +2494,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -2531,12 +2559,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2596,12 +2624,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2661,12 +2689,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2718,27 +2746,23 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>208.3</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2791,12 +2815,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2856,12 +2880,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2913,15 +2937,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>195.6</t>
+          <t>218.2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2974,20 +2998,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>194</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>218.9</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.04</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -3043,12 +3067,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -3095,25 +3119,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>129</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>150.1</t>
+          <t>160.8</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -3169,12 +3193,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>60.4</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3234,12 +3258,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>205.5</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -3287,27 +3311,23 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>170.7</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3347,32 +3367,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>138</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>284</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>224</v>
+        <v>283</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>126.2</t>
+          <t>236.5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>53.84</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3425,12 +3441,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>132.1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>42.28</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3482,27 +3498,23 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>217.6</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3542,7 +3554,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3555,12 +3567,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>233.0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1800.04</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -3603,7 +3615,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>146</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3616,12 +3628,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>245.6</t>
+          <t>309.1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1800.11</t>
+          <t>1800.00</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -3641,67 +3653,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3745,25 +3757,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -3828,7 +3840,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -3888,12 +3900,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -3958,7 +3970,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4018,12 +4030,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4083,12 +4095,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -4148,12 +4160,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4213,12 +4225,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>254.77</t>
+          <t>524.49</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4278,12 +4290,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4335,23 +4347,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>167.5</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1800.00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4391,28 +4407,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1800.02</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>12.49</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4465,12 +4485,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -4517,25 +4537,25 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>254.4</t>
+          <t>210.4</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1800.02</t>
+          <t>1800.08</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -4578,20 +4598,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>254.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -4652,12 +4672,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>117.2</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>84.06</t>
+          <t>77.84</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -4704,25 +4724,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>160</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>186.8</t>
+          <t>175.7</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.03</t>
+          <t>1800.07</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -4778,12 +4798,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -4830,25 +4850,25 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>368</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>230.3</t>
+          <t>201.3</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1800.03</t>
+          <t>1800.09</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -4896,25 +4916,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>386</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>196.8</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1800.09</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4954,28 +4976,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>337</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>423</v>
+        <v>336</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>282.8</t>
+          <t>159.5</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1800.06</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>173.13</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5028,12 +5054,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>172.30</t>
+          <t>123.91</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -5085,25 +5111,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>492</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>242.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1800.11</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5143,7 +5171,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5156,12 +5184,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>392.9</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1800.10</t>
+          <t>1800.06</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -5204,20 +5232,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>450</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>366.7</t>
+          <t>281.2</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -5242,67 +5270,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -5346,25 +5374,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -5429,7 +5457,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -5489,12 +5517,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -5559,7 +5587,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -5619,12 +5647,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -5684,12 +5712,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5749,12 +5777,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5814,12 +5842,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>524.49</t>
+          <t>254.77</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5879,12 +5907,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5936,27 +5964,23 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>167.5</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5996,32 +6020,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>12.49</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6074,12 +6094,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6126,25 +6146,25 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>313</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>210.4</t>
+          <t>254.4</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1800.08</t>
+          <t>1800.02</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -6187,20 +6207,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>313</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6261,12 +6281,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>117.2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>84.06</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6313,25 +6333,25 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>175.7</t>
+          <t>186.8</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1800.07</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -6387,12 +6407,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -6439,25 +6459,25 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>201.3</t>
+          <t>230.3</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1800.09</t>
+          <t>1800.03</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -6505,27 +6525,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>386</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>196.8</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6565,32 +6583,28 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>336</v>
+        <v>423</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>159.5</t>
+          <t>282.8</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>173.13</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.06</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6643,12 +6657,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>123.91</t>
+          <t>172.30</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -6700,27 +6714,25 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>492</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>242.5</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1800.11</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6760,7 +6772,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6773,12 +6785,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>392.9</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1800.06</t>
+          <t>1800.10</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -6821,20 +6833,20 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>169</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>457</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>281.2</t>
+          <t>366.7</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -6859,67 +6871,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -8476,67 +8488,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -10089,67 +10101,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Time limit (s)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>

--- a/experiments/results/cabp/cplex-cp-cabp.xlsx
+++ b/experiments/results/cabp/cplex-cp-cabp.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cabp_x1_no_hole" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11702,4 +11703,1601 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time limit (s)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Worker count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Best bound</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Best objective</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Best span</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Memory consumed (MB)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Time consumed (s)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Optimal found</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-pores_1.txt</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-pores_1.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>26</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>63.84</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-ibm32.txt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B-ibm32.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>31</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>13.6</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>33.61</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.txt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C-bcspwr01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>38</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D-bcsstk01.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>47</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.34</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.txt</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>E-bcspwr02.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>47</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-curtis54.txt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F-curtis54.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>49</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>12.4</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G-will57.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G-will57.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>54</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.txt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H-impcol_b.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>55</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>153.4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-ash85.txt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>I-ash85.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>84</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>65.39</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-nos4.txt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J-nos4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>99</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.txt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>K-dwt__234.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>116</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1800.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.txt</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L-bcspwr03.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>115</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.txt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M-bcsstk06.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>355.7</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1800.15</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.txt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N-bcsstk07.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>358.3</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1800.00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.txt</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>O-impcol_d.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>422</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>196.2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1800.11</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-can__445.txt</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-can__445.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>440</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>235.0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1800.08</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.txt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-494_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>493</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>179.9</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>550.38</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.txt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R-dwt__503.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>343.9</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1800.13</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S-sherman4.txt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S-sherman4.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>235.5</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1800.15</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.txt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T-dwt__592.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>581</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>331.5</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1800.22</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>U-662_bus.txt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U-662_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>659</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>280.5</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>669.86</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V-nos6.txt</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V-nos6.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>674</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>289.9</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1800.20</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>W-685_bus.txt</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W-685_bus.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>683</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>550.1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1800.09</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>X-can__715.txt</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>X-can__715.mtx.rnd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>621</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>513.6</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1800.30</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>